--- a/10_基础会计实训/10-E1_实训业务谁写哪几笔_v1.0_20260821.xlsx
+++ b/10_基础会计实训/10-E1_实训业务谁写哪几笔_v1.0_20260821.xlsx
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1 3 4 7 8 19 20 24 29 45</t>
+          <t>1 3 4 7 8 19 20 24 29 45 32</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>借款投资提现发工资还贷</t>
+          <t>借款投资提现发工资还贷、备用金</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>5 13 21 25 33 43</t>
+          <t>5 13 21 25 33 43 30</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>销售收入、收欠款、预收</t>
+          <t>销售收入、收欠款、预收、营业外收入</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>6 9 15 16 22 26 28 34 35 37</t>
+          <t>6 9 15 16 22 26 28 34 35 37 27 39 40 41 44</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>办公费宣传费利息捐赠等</t>
+          <t>办公费宣传费利息捐赠交税报销水电现金费用</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -678,10 +678,11 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>剩下列入费用组或资金组即可：27 交税 30 营业外收入 32 备用金 39 报销 40 41 水电 44 现金费用。不要再给利润组——利润必须全班写。</t>
+          <t>已分完：27 交税、39 报销、40 41 水电、44 现金费用→费用组；32 备用金→资金组；30 营业外收入→销售组。利润关仍是全班写 50–58。不要再单列利润组。</t>
         </is>
       </c>
     </row>
